--- a/data/trans_dic/IP12B$herida-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,21</t>
+          <t>0,0; 21,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,29</t>
+          <t>0,0; 53,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,43</t>
+          <t>0,0; 32,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,87</t>
+          <t>0,0; 16,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,01</t>
+          <t>0,0; 12,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,62</t>
+          <t>0,0; 27,64</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,33</t>
+          <t>0,0; 13,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,25</t>
+          <t>0,0; 18,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,24</t>
+          <t>0,0; 19,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,17</t>
+          <t>0,0; 28,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 30,49</t>
+          <t>0,0; 29,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,12</t>
+          <t>0,0; 11,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 17,55</t>
+          <t>1,84; 15,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 18,3</t>
+          <t>3,34; 17,89</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,95</t>
+          <t>0,0; 24,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,15</t>
+          <t>0,0; 28,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,97</t>
+          <t>0,0; 25,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 30,29</t>
+          <t>3,51; 31,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,24</t>
+          <t>0,0; 15,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,08</t>
+          <t>0,0; 20,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 21,46</t>
+          <t>3,96; 22,15</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,98</t>
+          <t>0,0; 46,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,8</t>
+          <t>0,0; 29,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,44</t>
+          <t>0,0; 22,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,09</t>
+          <t>0,0; 26,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,57</t>
+          <t>0,0; 12,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,1</t>
+          <t>0,0; 9,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,51</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 13,28</t>
+          <t>2,09; 13,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,2</t>
+          <t>1,47; 12,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 14,3</t>
+          <t>2,36; 13,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,71</t>
+          <t>2,75; 16,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,81</t>
+          <t>1,57; 8,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 8,49</t>
+          <t>1,81; 8,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,0</t>
+          <t>3,57; 11,51</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3616</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4770</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3844</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3949</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3403</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4419</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1941</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2675</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3802</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3103</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3985</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4665</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3111</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>614; 5254</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1197; 6410</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2936</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3072</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3352</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4566</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>560; 4990</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3311</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5531</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1090; 6100</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3198</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3085</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4684</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4551</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4511</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3576</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5228</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7146</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4230</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4015</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1151; 7592</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>685; 5818</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1499; 8841</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1318; 7746</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1426; 7980</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2255; 10719</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3680; 11856</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$herida-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,17 +683,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,09</t>
+          <t>0,0; 18,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,77</t>
+          <t>0,0; 46,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,61</t>
+          <t>0,0; 28,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,44</t>
+          <t>0,0; 15,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,44</t>
+          <t>0,0; 10,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,64</t>
+          <t>0,0; 37,52</t>
         </is>
       </c>
     </row>
@@ -793,42 +793,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,95</t>
+          <t>0,0; 19,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,75</t>
+          <t>0,0; 20,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,22</t>
+          <t>0,0; 21,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,21</t>
+          <t>0,0; 30,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,99</t>
+          <t>3,87; 30,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,01</t>
+          <t>0,0; 13,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 15,77</t>
+          <t>1,82; 15,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 17,89</t>
+          <t>3,36; 18,68</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,19</t>
+          <t>0,0; 24,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,92</t>
+          <t>0,0; 31,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,27 +918,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,2</t>
+          <t>0,0; 29,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 31,3</t>
+          <t>3,54; 30,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,79</t>
+          <t>0,0; 16,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,09</t>
+          <t>0,0; 17,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 22,15</t>
+          <t>4,12; 22,92</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,73</t>
+          <t>0,0; 45,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,39</t>
+          <t>0,0; 26,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,2</t>
+          <t>0,0; 23,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,24</t>
+          <t>0,0; 25,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,31</t>
+          <t>0,0; 13,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,64</t>
+          <t>0,0; 9,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 13,77</t>
+          <t>2,18; 13,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,46</t>
+          <t>1,47; 11,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 13,91</t>
+          <t>1,96; 13,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 16,18</t>
+          <t>2,68; 14,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,81</t>
+          <t>1,44; 8,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,59</t>
+          <t>1,75; 7,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 11,51</t>
+          <t>3,59; 11,61</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3616</t>
+          <t>0; 3138</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4770</t>
+          <t>0; 4090</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3844</t>
+          <t>0; 3302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3949</t>
+          <t>0; 3647</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3403</t>
+          <t>0; 2956</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4419</t>
+          <t>0; 6000</t>
         </is>
       </c>
     </row>
@@ -1585,42 +1585,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2675</t>
+          <t>0; 3700</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3802</t>
+          <t>0; 4090</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3103</t>
+          <t>0; 3506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3985</t>
+          <t>0; 4271</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4665</t>
+          <t>603; 4743</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3111</t>
+          <t>0; 3706</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>614; 5254</t>
+          <t>606; 5270</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1197; 6410</t>
+          <t>1204; 6693</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3072</t>
+          <t>0; 3141</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3352</t>
+          <t>0; 3635</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1763,27 +1763,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4566</t>
+          <t>0; 5361</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>560; 4990</t>
+          <t>564; 4904</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3311</t>
+          <t>0; 3546</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5531</t>
+          <t>0; 4814</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1090; 6100</t>
+          <t>1134; 6311</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3198</t>
+          <t>0; 3147</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3085</t>
+          <t>0; 2802</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4684</t>
+          <t>0; 4974</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4551</t>
+          <t>0; 4467</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4511</t>
+          <t>0; 4930</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4230</t>
+          <t>0; 4251</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4015</t>
+          <t>0; 4139</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1151; 7592</t>
+          <t>1200; 7458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>685; 5818</t>
+          <t>686; 5499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1499; 8841</t>
+          <t>1248; 8726</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1318; 7746</t>
+          <t>1284; 7162</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1426; 7980</t>
+          <t>1306; 7770</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2255; 10719</t>
+          <t>2181; 9965</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3680; 11856</t>
+          <t>3701; 11959</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$herida-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,07%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12,39%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 27,43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 18,31</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 50,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,18</t>
+          <t>0,0; 15,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,81</t>
+          <t>0,0; 13,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,52</t>
+          <t>0,0; 31,62</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>3,42%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,77%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 21,24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 31,17</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3,91; 30,49</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 19,29</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 20,17</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 21,72</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,24</t>
+          <t>0,0; 17,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 30,49</t>
+          <t>0,0; 18,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,12</t>
+          <t>0,0; 12,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 15,82</t>
+          <t>1,86; 17,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 18,68</t>
+          <t>3,33; 18,3</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,83%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,65%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 24,97</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3,53; 30,29</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 24,95</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 31,36</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 29,59</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 30,76</t>
+          <t>0,0; 29,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,91</t>
+          <t>0,0; 14,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,49</t>
+          <t>0,0; 18,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 22,92</t>
+          <t>3,74; 21,46</t>
         </is>
       </c>
     </row>
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>11,35%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,29 +1008,29 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,97</t>
+          <t>0,0; 35,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 22,44</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 45,98</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 26,7</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 23,57</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,76</t>
+          <t>0,0; 26,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,45</t>
+          <t>0,0; 12,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,17%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,21%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,15%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,69</t>
+          <t>1,44; 12,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>2,18; 14,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 13,53</t>
+          <t>2,7; 15,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 11,77</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 13,73</t>
+          <t>0,0; 7,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 14,96</t>
+          <t>2,05; 13,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,58</t>
+          <t>1,52; 8,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,98</t>
+          <t>1,94; 8,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 11,61</t>
+          <t>3,68; 12,0</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>697</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1099</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3233</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3138</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4090</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3302</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3636</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4462</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3647</t>
+          <t>0; 3813</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2956</t>
+          <t>0; 3559</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6000</t>
+          <t>0; 5056</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1941</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1169</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1403</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1941</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0; 3430</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4403</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>608; 4743</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3700</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4090</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3506</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4271</t>
+          <t>0; 3324</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>603; 4743</t>
+          <t>0; 3701</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3706</t>
+          <t>0; 3422</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>606; 5270</t>
+          <t>619; 5846</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1204; 6693</t>
+          <t>1192; 6557</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1119</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1531</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1817</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3141</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0; 4524</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>563; 4828</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3167</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3635</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 5361</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>564; 4904</t>
+          <t>0; 3379</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3546</t>
+          <t>0; 2987</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4814</t>
+          <t>0; 4978</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1134; 6311</t>
+          <t>1030; 5908</t>
         </is>
       </c>
     </row>
@@ -1805,22 +1805,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,27 +1853,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>777</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1906,29 +1906,29 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3147</t>
+          <t>0; 3757</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>0; 4737</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3148</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0; 2802</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4974</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4467</t>
+          <t>0; 4523</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4930</t>
+          <t>0; 4608</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1389</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1353</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3388</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3875</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3759</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4251</t>
+          <t>674; 5700</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4139</t>
+          <t>1385; 9087</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1200; 7458</t>
+          <t>1293; 7517</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>686; 5499</t>
+          <t>0; 4432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1248; 8726</t>
+          <t>0; 4605</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1284; 7162</t>
+          <t>1129; 7318</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1306; 7770</t>
+          <t>1378; 7981</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2181; 9965</t>
+          <t>2418; 10596</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3701; 11959</t>
+          <t>3787; 12362</t>
         </is>
       </c>
     </row>
